--- a/ckanext/lhm/schemas/template_plandb.xlsx
+++ b/ckanext/lhm/schemas/template_plandb.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\home\mb\p2\ckanext-lhm\ckanext\lhm\schemas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{174A4BB7-77B0-4316-A50E-A1F3EF41E677}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67598EC1-9D7C-4B86-8ADD-11DFD583A73D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="871" xr2:uid="{EFAD0BDA-2C19-4F99-80E8-84599936D919}"/>
   </bookViews>
@@ -788,15 +788,9 @@
     <t>PLAN_MD_update-zyklus</t>
   </si>
   <si>
-    <t>quartalsweise</t>
-  </si>
-  <si>
     <t>Jährlich</t>
   </si>
   <si>
-    <t>zweijährlich</t>
-  </si>
-  <si>
     <t>PLAN_MD_schema</t>
   </si>
   <si>
@@ -855,6 +849,12 @@
   </si>
   <si>
     <t>ZEN</t>
+  </si>
+  <si>
+    <t>Quartalsweise</t>
+  </si>
+  <si>
+    <t>Zweijährlich</t>
   </si>
 </sst>
 </file>
@@ -1121,14 +1121,14 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1923,7 +1923,7 @@
       <c r="K30" s="19"/>
     </row>
     <row r="31" spans="1:12">
-      <c r="A31" s="31" t="s">
+      <c r="A31" s="29" t="s">
         <v>103</v>
       </c>
       <c r="B31" s="19"/>
@@ -2014,60 +2014,60 @@
       </c>
     </row>
     <row r="40" spans="1:12">
-      <c r="A40" s="29" t="s">
+      <c r="A40" s="30" t="s">
         <v>191</v>
       </c>
-      <c r="B40" s="30"/>
-      <c r="C40" s="30"/>
-      <c r="D40" s="30"/>
+      <c r="B40" s="31"/>
+      <c r="C40" s="31"/>
+      <c r="D40" s="31"/>
     </row>
     <row r="41" spans="1:12">
-      <c r="A41" s="30"/>
-      <c r="B41" s="30"/>
-      <c r="C41" s="30"/>
-      <c r="D41" s="30"/>
+      <c r="A41" s="31"/>
+      <c r="B41" s="31"/>
+      <c r="C41" s="31"/>
+      <c r="D41" s="31"/>
     </row>
     <row r="42" spans="1:12">
-      <c r="A42" s="30"/>
-      <c r="B42" s="30"/>
-      <c r="C42" s="30"/>
-      <c r="D42" s="30"/>
+      <c r="A42" s="31"/>
+      <c r="B42" s="31"/>
+      <c r="C42" s="31"/>
+      <c r="D42" s="31"/>
     </row>
     <row r="43" spans="1:12">
-      <c r="A43" s="30"/>
-      <c r="B43" s="30"/>
-      <c r="C43" s="30"/>
-      <c r="D43" s="30"/>
+      <c r="A43" s="31"/>
+      <c r="B43" s="31"/>
+      <c r="C43" s="31"/>
+      <c r="D43" s="31"/>
     </row>
     <row r="44" spans="1:12">
-      <c r="A44" s="30"/>
-      <c r="B44" s="30"/>
-      <c r="C44" s="30"/>
-      <c r="D44" s="30"/>
+      <c r="A44" s="31"/>
+      <c r="B44" s="31"/>
+      <c r="C44" s="31"/>
+      <c r="D44" s="31"/>
     </row>
     <row r="45" spans="1:12">
-      <c r="A45" s="30"/>
-      <c r="B45" s="30"/>
-      <c r="C45" s="30"/>
-      <c r="D45" s="30"/>
+      <c r="A45" s="31"/>
+      <c r="B45" s="31"/>
+      <c r="C45" s="31"/>
+      <c r="D45" s="31"/>
     </row>
     <row r="46" spans="1:12">
-      <c r="A46" s="30"/>
-      <c r="B46" s="30"/>
-      <c r="C46" s="30"/>
-      <c r="D46" s="30"/>
+      <c r="A46" s="31"/>
+      <c r="B46" s="31"/>
+      <c r="C46" s="31"/>
+      <c r="D46" s="31"/>
     </row>
     <row r="47" spans="1:12">
-      <c r="A47" s="30"/>
-      <c r="B47" s="30"/>
-      <c r="C47" s="30"/>
-      <c r="D47" s="30"/>
+      <c r="A47" s="31"/>
+      <c r="B47" s="31"/>
+      <c r="C47" s="31"/>
+      <c r="D47" s="31"/>
     </row>
     <row r="48" spans="1:12">
-      <c r="A48" s="30"/>
-      <c r="B48" s="30"/>
-      <c r="C48" s="30"/>
-      <c r="D48" s="30"/>
+      <c r="A48" s="31"/>
+      <c r="B48" s="31"/>
+      <c r="C48" s="31"/>
+      <c r="D48" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2328,7 +2328,7 @@
         <v>226</v>
       </c>
       <c r="W1" s="5" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="X1" s="5" t="s">
         <v>240</v>
@@ -2398,7 +2398,7 @@
         <v>227</v>
       </c>
       <c r="W2" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="X2" s="2" t="s">
         <v>104</v>
@@ -2472,7 +2472,7 @@
         <v>228</v>
       </c>
       <c r="W3" s="3" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="X3" s="2" t="s">
         <v>143</v>
@@ -2537,7 +2537,7 @@
         <v>239</v>
       </c>
       <c r="W4" s="3" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="X4" s="2" t="s">
         <v>144</v>
@@ -2581,7 +2581,7 @@
         <v>90</v>
       </c>
       <c r="W5" s="3" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="X5" s="2" t="s">
         <v>145</v>
@@ -2625,7 +2625,7 @@
         <v>193</v>
       </c>
       <c r="W6" s="3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="X6" s="2" t="s">
         <v>146</v>
@@ -2663,7 +2663,7 @@
         <v>192</v>
       </c>
       <c r="W7" s="3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="X7" s="2" t="s">
         <v>105</v>
@@ -2701,10 +2701,10 @@
         <v>194</v>
       </c>
       <c r="W8" s="3" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="X8" s="2" t="s">
-        <v>241</v>
+        <v>262</v>
       </c>
     </row>
     <row r="9" spans="1:24">
@@ -2728,10 +2728,10 @@
         <v>196</v>
       </c>
       <c r="W9" s="3" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="X9" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="10" spans="1:24">
@@ -2756,10 +2756,10 @@
         <v>195</v>
       </c>
       <c r="W10" s="3" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="X10" s="2" t="s">
-        <v>243</v>
+        <v>263</v>
       </c>
     </row>
     <row r="11" spans="1:24">
@@ -2784,7 +2784,7 @@
         <v>197</v>
       </c>
       <c r="W11" s="3" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="X11" s="2" t="s">
         <v>106</v>
@@ -2806,7 +2806,7 @@
         <v>198</v>
       </c>
       <c r="W12" s="3" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="13" spans="1:24">
@@ -2822,7 +2822,7 @@
       <c r="E13" s="1"/>
       <c r="K13" s="15"/>
       <c r="W13" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="14" spans="1:24">
@@ -2838,7 +2838,7 @@
       <c r="E14" s="1"/>
       <c r="K14" s="15"/>
       <c r="W14" s="3" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="15" spans="1:24">
@@ -2854,7 +2854,7 @@
       <c r="E15" s="1"/>
       <c r="K15" s="15"/>
       <c r="W15" s="3" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="16" spans="1:24">
@@ -2870,7 +2870,7 @@
       <c r="E16" s="1"/>
       <c r="K16" s="15"/>
       <c r="W16" s="3" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="17" spans="1:23">
@@ -2886,7 +2886,7 @@
       <c r="E17" s="1"/>
       <c r="K17" s="15"/>
       <c r="W17" s="3" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="18" spans="1:23">
@@ -2918,7 +2918,7 @@
       <c r="E19" s="1"/>
       <c r="K19" s="15"/>
       <c r="W19" s="3" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="20" spans="1:23">
@@ -2934,7 +2934,7 @@
       <c r="E20" s="1"/>
       <c r="K20" s="15"/>
       <c r="W20" s="3" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="21" spans="1:23">
@@ -2950,7 +2950,7 @@
       <c r="E21" s="1"/>
       <c r="K21" s="15"/>
       <c r="W21" s="3" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="22" spans="1:23">
@@ -3045,7 +3045,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="PH4zrp7eXCCYTe30bZgWa4oN323isiTnw119OHfSlXEE4aKSPiWff8viQcR9grAl1yuVHM8VUpNSbGDq2VjIJA==" saltValue="JZVoZuV7oNQazjtxqkPBpg==" spinCount="100000" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="IoNONSJZWHkpB1oTfpzhCzNP+Zio50vimJ07ZuJhhqfK79beNOBBs62YZ6Yq9RFLv9Z3Yf+u0zXNIbmm/UvHgQ==" saltValue="g1R9BJJ9ENWepKSLFgV4GQ==" spinCount="100000" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/ckanext/lhm/schemas/template_plandb.xlsx
+++ b/ckanext/lhm/schemas/template_plandb.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\home\mb\p2\ckanext-lhm\ckanext\lhm\schemas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67598EC1-9D7C-4B86-8ADD-11DFD583A73D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D11B828-6F1D-4757-8C76-F4681552451D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="871" xr2:uid="{EFAD0BDA-2C19-4F99-80E8-84599936D919}"/>
+    <workbookView xWindow="1092" yWindow="972" windowWidth="21792" windowHeight="10788" tabRatio="871" xr2:uid="{EFAD0BDA-2C19-4F99-80E8-84599936D919}"/>
   </bookViews>
   <sheets>
     <sheet name="Metadaten" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="266">
   <si>
     <t>nein</t>
   </si>
@@ -758,9 +758,6 @@
     <t>Bedeutung</t>
   </si>
   <si>
-    <t>1.3.2.</t>
-  </si>
-  <si>
     <t>ArcGIS Map Service</t>
   </si>
   <si>
@@ -855,6 +852,15 @@
   </si>
   <si>
     <t>Zweijährlich</t>
+  </si>
+  <si>
+    <t>WMTS-KVP</t>
+  </si>
+  <si>
+    <t>Link</t>
+  </si>
+  <si>
+    <t>1.3.3.</t>
   </si>
 </sst>
 </file>
@@ -1121,14 +1127,14 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1685,7 +1691,7 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="16" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B14" s="21"/>
       <c r="C14" s="12"/>
@@ -1700,7 +1706,7 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="16" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B15" s="21"/>
       <c r="C15" s="12"/>
@@ -1715,7 +1721,7 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B16" s="21"/>
       <c r="C16" s="12"/>
@@ -1805,14 +1811,14 @@
     </row>
     <row r="22" spans="1:12">
       <c r="A22" s="16" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B22" s="21"/>
       <c r="K22" s="17"/>
     </row>
     <row r="23" spans="1:12">
       <c r="A23" s="16" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B23" s="21"/>
       <c r="K23" s="17"/>
@@ -1923,7 +1929,7 @@
       <c r="K30" s="19"/>
     </row>
     <row r="31" spans="1:12">
-      <c r="A31" s="29" t="s">
+      <c r="A31" s="31" t="s">
         <v>103</v>
       </c>
       <c r="B31" s="19"/>
@@ -1990,7 +1996,7 @@
         <v>200</v>
       </c>
       <c r="B35" s="26" t="s">
-        <v>231</v>
+        <v>265</v>
       </c>
       <c r="C35" s="12"/>
       <c r="D35" s="12"/>
@@ -2014,60 +2020,60 @@
       </c>
     </row>
     <row r="40" spans="1:12">
-      <c r="A40" s="30" t="s">
+      <c r="A40" s="29" t="s">
         <v>191</v>
       </c>
-      <c r="B40" s="31"/>
-      <c r="C40" s="31"/>
-      <c r="D40" s="31"/>
+      <c r="B40" s="30"/>
+      <c r="C40" s="30"/>
+      <c r="D40" s="30"/>
     </row>
     <row r="41" spans="1:12">
-      <c r="A41" s="31"/>
-      <c r="B41" s="31"/>
-      <c r="C41" s="31"/>
-      <c r="D41" s="31"/>
+      <c r="A41" s="30"/>
+      <c r="B41" s="30"/>
+      <c r="C41" s="30"/>
+      <c r="D41" s="30"/>
     </row>
     <row r="42" spans="1:12">
-      <c r="A42" s="31"/>
-      <c r="B42" s="31"/>
-      <c r="C42" s="31"/>
-      <c r="D42" s="31"/>
+      <c r="A42" s="30"/>
+      <c r="B42" s="30"/>
+      <c r="C42" s="30"/>
+      <c r="D42" s="30"/>
     </row>
     <row r="43" spans="1:12">
-      <c r="A43" s="31"/>
-      <c r="B43" s="31"/>
-      <c r="C43" s="31"/>
-      <c r="D43" s="31"/>
+      <c r="A43" s="30"/>
+      <c r="B43" s="30"/>
+      <c r="C43" s="30"/>
+      <c r="D43" s="30"/>
     </row>
     <row r="44" spans="1:12">
-      <c r="A44" s="31"/>
-      <c r="B44" s="31"/>
-      <c r="C44" s="31"/>
-      <c r="D44" s="31"/>
+      <c r="A44" s="30"/>
+      <c r="B44" s="30"/>
+      <c r="C44" s="30"/>
+      <c r="D44" s="30"/>
     </row>
     <row r="45" spans="1:12">
-      <c r="A45" s="31"/>
-      <c r="B45" s="31"/>
-      <c r="C45" s="31"/>
-      <c r="D45" s="31"/>
+      <c r="A45" s="30"/>
+      <c r="B45" s="30"/>
+      <c r="C45" s="30"/>
+      <c r="D45" s="30"/>
     </row>
     <row r="46" spans="1:12">
-      <c r="A46" s="31"/>
-      <c r="B46" s="31"/>
-      <c r="C46" s="31"/>
-      <c r="D46" s="31"/>
+      <c r="A46" s="30"/>
+      <c r="B46" s="30"/>
+      <c r="C46" s="30"/>
+      <c r="D46" s="30"/>
     </row>
     <row r="47" spans="1:12">
-      <c r="A47" s="31"/>
-      <c r="B47" s="31"/>
-      <c r="C47" s="31"/>
-      <c r="D47" s="31"/>
+      <c r="A47" s="30"/>
+      <c r="B47" s="30"/>
+      <c r="C47" s="30"/>
+      <c r="D47" s="30"/>
     </row>
     <row r="48" spans="1:12">
-      <c r="A48" s="31"/>
-      <c r="B48" s="31"/>
-      <c r="C48" s="31"/>
-      <c r="D48" s="31"/>
+      <c r="A48" s="30"/>
+      <c r="B48" s="30"/>
+      <c r="C48" s="30"/>
+      <c r="D48" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2328,10 +2334,10 @@
         <v>226</v>
       </c>
       <c r="W1" s="5" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="X1" s="5" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="2" spans="1:24">
@@ -2398,7 +2404,7 @@
         <v>227</v>
       </c>
       <c r="W2" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="X2" s="2" t="s">
         <v>104</v>
@@ -2472,7 +2478,7 @@
         <v>228</v>
       </c>
       <c r="W3" s="3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="X3" s="2" t="s">
         <v>143</v>
@@ -2534,10 +2540,10 @@
         <v>91</v>
       </c>
       <c r="V4" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="W4" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="X4" s="2" t="s">
         <v>144</v>
@@ -2581,7 +2587,7 @@
         <v>90</v>
       </c>
       <c r="W5" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="X5" s="2" t="s">
         <v>145</v>
@@ -2625,7 +2631,7 @@
         <v>193</v>
       </c>
       <c r="W6" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="X6" s="2" t="s">
         <v>146</v>
@@ -2657,13 +2663,13 @@
         <v>197</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>99</v>
+        <v>263</v>
       </c>
       <c r="U7" s="2" t="s">
         <v>192</v>
       </c>
       <c r="W7" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="X7" s="2" t="s">
         <v>105</v>
@@ -2695,16 +2701,16 @@
         <v>93</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="U8" s="2" t="s">
         <v>194</v>
       </c>
       <c r="W8" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="X8" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="9" spans="1:24">
@@ -2722,16 +2728,16 @@
         <v>119</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>232</v>
+        <v>100</v>
       </c>
       <c r="U9" s="2" t="s">
         <v>196</v>
       </c>
       <c r="W9" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="X9" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="10" spans="1:24">
@@ -2750,16 +2756,16 @@
       </c>
       <c r="K10" s="15"/>
       <c r="R10" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="U10" s="2" t="s">
         <v>195</v>
       </c>
       <c r="W10" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="X10" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="11" spans="1:24">
@@ -2778,13 +2784,13 @@
       </c>
       <c r="K11" s="15"/>
       <c r="R11" s="2" t="s">
-        <v>86</v>
+        <v>232</v>
       </c>
       <c r="U11" s="2" t="s">
         <v>197</v>
       </c>
       <c r="W11" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="X11" s="2" t="s">
         <v>106</v>
@@ -2802,11 +2808,14 @@
       </c>
       <c r="E12" s="1"/>
       <c r="K12" s="15"/>
+      <c r="R12" s="2" t="s">
+        <v>86</v>
+      </c>
       <c r="U12" s="2" t="s">
         <v>198</v>
       </c>
       <c r="W12" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="13" spans="1:24">
@@ -2821,8 +2830,11 @@
       </c>
       <c r="E13" s="1"/>
       <c r="K13" s="15"/>
+      <c r="R13" s="2" t="s">
+        <v>264</v>
+      </c>
       <c r="W13" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="14" spans="1:24">
@@ -2838,7 +2850,7 @@
       <c r="E14" s="1"/>
       <c r="K14" s="15"/>
       <c r="W14" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="15" spans="1:24">
@@ -2854,7 +2866,7 @@
       <c r="E15" s="1"/>
       <c r="K15" s="15"/>
       <c r="W15" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="16" spans="1:24">
@@ -2870,7 +2882,7 @@
       <c r="E16" s="1"/>
       <c r="K16" s="15"/>
       <c r="W16" s="3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="17" spans="1:23">
@@ -2886,7 +2898,7 @@
       <c r="E17" s="1"/>
       <c r="K17" s="15"/>
       <c r="W17" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="18" spans="1:23">
@@ -2918,7 +2930,7 @@
       <c r="E19" s="1"/>
       <c r="K19" s="15"/>
       <c r="W19" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="1:23">
@@ -2934,7 +2946,7 @@
       <c r="E20" s="1"/>
       <c r="K20" s="15"/>
       <c r="W20" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="1:23">
@@ -2950,7 +2962,7 @@
       <c r="E21" s="1"/>
       <c r="K21" s="15"/>
       <c r="W21" s="3" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="1:23">
@@ -3045,7 +3057,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="IoNONSJZWHkpB1oTfpzhCzNP+Zio50vimJ07ZuJhhqfK79beNOBBs62YZ6Yq9RFLv9Z3Yf+u0zXNIbmm/UvHgQ==" saltValue="g1R9BJJ9ENWepKSLFgV4GQ==" spinCount="100000" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="ilEvpGmLo6a2O3ZAU+i9yQGGscrus6aYietO82VMOaIJdasi+nuCz4K4VGwvF5eoMx2reLQ9A/c/BCnrtsR9rw==" saltValue="4P2QQwj56WNptjDpbIU8kA==" spinCount="100000" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/ckanext/lhm/schemas/template_plandb.xlsx
+++ b/ckanext/lhm/schemas/template_plandb.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr codeName="DieseArbeitsmappe" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\home\mb\p2\ckanext-lhm\ckanext\lhm\schemas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\home\mb\dev\ckanext-lhm\ckanext\lhm\schemas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D11B828-6F1D-4757-8C76-F4681552451D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA04A1C9-E5AE-40D9-95B4-38CAF35AC083}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1092" yWindow="972" windowWidth="21792" windowHeight="10788" tabRatio="871" xr2:uid="{EFAD0BDA-2C19-4F99-80E8-84599936D919}"/>
+    <workbookView xWindow="24" yWindow="384" windowWidth="23016" windowHeight="12108" tabRatio="871" xr2:uid="{EFAD0BDA-2C19-4F99-80E8-84599936D919}"/>
   </bookViews>
   <sheets>
     <sheet name="Metadaten" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="Wertelisten" sheetId="16" state="hidden" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Metadaten!$A$1:$K$48</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Metadaten!$A$1:$K$49</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="267">
   <si>
     <t>nein</t>
   </si>
@@ -259,9 +259,6 @@
   </si>
   <si>
     <t>Wert 10</t>
-  </si>
-  <si>
-    <t>Organisation *</t>
   </si>
   <si>
     <t>Externe Datenurheber *</t>
@@ -860,7 +857,13 @@
     <t>Link</t>
   </si>
   <si>
-    <t>1.3.3.</t>
+    <t>Abteilung *</t>
+  </si>
+  <si>
+    <t>1.3.6.</t>
+  </si>
+  <si>
+    <t>Metadatenschema *</t>
   </si>
 </sst>
 </file>
@@ -1462,7 +1465,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{860E5F97-3212-47C5-A469-BCE2C1CB3CAC}">
   <sheetPr codeName="Tabelle1"/>
-  <dimension ref="A1:L48"/>
+  <dimension ref="A1:L49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="48.5" style="14" customWidth="1"/>
@@ -1511,7 +1514,7 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="18" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B2" s="19"/>
       <c r="C2" s="12"/>
@@ -1526,7 +1529,7 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B3" s="19"/>
       <c r="C3" s="12"/>
@@ -1541,7 +1544,7 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="11" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B4" s="20"/>
       <c r="C4" s="12"/>
@@ -1556,7 +1559,7 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B5" s="21"/>
       <c r="C5" s="23"/>
@@ -1571,7 +1574,7 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="16" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B6" s="21"/>
       <c r="C6" s="21"/>
@@ -1586,7 +1589,7 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="11" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B7" s="19"/>
       <c r="C7" s="12"/>
@@ -1601,7 +1604,7 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="11" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B8" s="19"/>
       <c r="C8" s="12"/>
@@ -1631,7 +1634,7 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="16" t="s">
-        <v>71</v>
+        <v>264</v>
       </c>
       <c r="B10" s="21"/>
       <c r="C10" s="12"/>
@@ -1646,7 +1649,7 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B11" s="21"/>
       <c r="C11" s="12"/>
@@ -1661,7 +1664,7 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B12" s="22"/>
       <c r="C12" s="12"/>
@@ -1676,7 +1679,7 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B13" s="21"/>
       <c r="C13" s="12"/>
@@ -1691,7 +1694,7 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="16" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B14" s="21"/>
       <c r="C14" s="12"/>
@@ -1706,7 +1709,7 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="16" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B15" s="21"/>
       <c r="C15" s="12"/>
@@ -1721,7 +1724,7 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="16" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B16" s="21"/>
       <c r="C16" s="12"/>
@@ -1736,7 +1739,7 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B17" s="19"/>
       <c r="C17" s="12"/>
@@ -1751,7 +1754,7 @@
     </row>
     <row r="18" spans="1:12">
       <c r="A18" s="11" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B18" s="19"/>
       <c r="C18" s="12"/>
@@ -1781,7 +1784,7 @@
     </row>
     <row r="20" spans="1:12">
       <c r="A20" s="16" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B20" s="21"/>
       <c r="C20" s="12"/>
@@ -1796,7 +1799,7 @@
     </row>
     <row r="21" spans="1:12">
       <c r="A21" s="16" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B21" s="21"/>
       <c r="C21" s="12"/>
@@ -1811,21 +1814,21 @@
     </row>
     <row r="22" spans="1:12">
       <c r="A22" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B22" s="21"/>
       <c r="K22" s="17"/>
     </row>
     <row r="23" spans="1:12">
       <c r="A23" s="16" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B23" s="21"/>
       <c r="K23" s="17"/>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" s="16" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B24" s="21"/>
       <c r="C24" s="12"/>
@@ -1840,7 +1843,7 @@
     </row>
     <row r="25" spans="1:12">
       <c r="A25" s="16" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B25" s="21"/>
       <c r="C25" s="21"/>
@@ -1855,7 +1858,7 @@
     </row>
     <row r="26" spans="1:12">
       <c r="A26" s="16" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B26" s="21"/>
       <c r="C26" s="12"/>
@@ -1870,7 +1873,7 @@
     </row>
     <row r="27" spans="1:12">
       <c r="A27" s="16" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B27" s="21"/>
       <c r="C27" s="12"/>
@@ -1885,7 +1888,7 @@
     </row>
     <row r="28" spans="1:12">
       <c r="A28" s="16" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B28" s="21"/>
       <c r="C28" s="12"/>
@@ -1900,7 +1903,7 @@
     </row>
     <row r="29" spans="1:12">
       <c r="A29" s="16" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B29" s="21"/>
       <c r="C29" s="12"/>
@@ -1915,7 +1918,7 @@
     </row>
     <row r="30" spans="1:12">
       <c r="A30" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B30" s="19"/>
       <c r="C30" s="24"/>
@@ -1930,7 +1933,7 @@
     </row>
     <row r="31" spans="1:12">
       <c r="A31" s="31" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B31" s="19"/>
       <c r="C31" s="24"/>
@@ -1945,7 +1948,7 @@
     </row>
     <row r="32" spans="1:12">
       <c r="A32" s="14" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B32" s="25"/>
       <c r="C32" s="12"/>
@@ -1961,7 +1964,7 @@
     </row>
     <row r="33" spans="1:12">
       <c r="A33" s="14" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B33" s="26"/>
       <c r="C33" s="12"/>
@@ -1977,7 +1980,7 @@
     </row>
     <row r="34" spans="1:12">
       <c r="A34" s="14" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B34" s="26"/>
       <c r="C34" s="12"/>
@@ -1993,11 +1996,9 @@
     </row>
     <row r="35" spans="1:12">
       <c r="A35" s="14" t="s">
-        <v>200</v>
-      </c>
-      <c r="B35" s="26" t="s">
-        <v>265</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="B35" s="26"/>
       <c r="C35" s="12"/>
       <c r="D35" s="12"/>
       <c r="E35" s="12"/>
@@ -2009,26 +2010,38 @@
       <c r="K35" s="12"/>
       <c r="L35" s="12"/>
     </row>
-    <row r="37" spans="1:12">
-      <c r="A37" s="14" t="s">
-        <v>75</v>
-      </c>
+    <row r="36" spans="1:12">
+      <c r="A36" s="14" t="s">
+        <v>199</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>265</v>
+      </c>
+      <c r="C36" s="12"/>
+      <c r="D36" s="12"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="12"/>
+      <c r="G36" s="12"/>
+      <c r="H36" s="12"/>
+      <c r="I36" s="12"/>
+      <c r="J36" s="12"/>
+      <c r="K36" s="12"/>
+      <c r="L36" s="12"/>
     </row>
     <row r="38" spans="1:12">
       <c r="A38" s="14" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12">
-      <c r="A40" s="29" t="s">
-        <v>191</v>
-      </c>
-      <c r="B40" s="30"/>
-      <c r="C40" s="30"/>
-      <c r="D40" s="30"/>
+        <v>74</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12">
+      <c r="A39" s="14" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="41" spans="1:12">
-      <c r="A41" s="30"/>
+      <c r="A41" s="29" t="s">
+        <v>190</v>
+      </c>
       <c r="B41" s="30"/>
       <c r="C41" s="30"/>
       <c r="D41" s="30"/>
@@ -2075,12 +2088,18 @@
       <c r="C48" s="30"/>
       <c r="D48" s="30"/>
     </row>
+    <row r="49" spans="1:4">
+      <c r="A49" s="30"/>
+      <c r="B49" s="30"/>
+      <c r="C49" s="30"/>
+      <c r="D49" s="30"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A40:D48"/>
+    <mergeCell ref="A41:D49"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations xWindow="1350" yWindow="369" count="34">
+  <dataValidations xWindow="1350" yWindow="369" count="35">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Thema | NAME_DER_TABELLE." prompt="Der Titel beteht aus dem Thema (für Geodatenpool: ehemals Datenbestand) und dem Namen der Tabelle in der Datenbank." sqref="B2" xr:uid="{7CC76290-C397-4A0D-82F8-39029843BD91}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Klare und prägnante Beschreibung des Datensatzes, damit auch Laien den Inhalt verstehen und einschätzen können. Dazu können neben dem konkreten Inhalt z.B. die räumliche Abdeckung, Vollständigkeit, Urheberschaft und Aktualität gehören." sqref="B4" xr:uid="{F0D16E7B-F9FC-4508-96CB-4EA176A334B4}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Schlagworte sind i.d.R. Substantive zur inhaltlichen Beschreibung des Datensatzes. Es können mehrere Schlagworte vergeben werden." sqref="B5" xr:uid="{623C178E-EC83-43E9-958F-0440F931AA20}"/>
@@ -2109,12 +2128,13 @@
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Angabe der Team-E-Mailadresse des Datenverantwortlichen" sqref="B12" xr:uid="{BE4AF42B-6330-4B78-96B6-38C329A34190}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Mit High Value Datasets sind Daten gemeint, die in unter die DVO-HVD fallen. HVD-Daten sind per Definition immer auch Open Data." sqref="B27" xr:uid="{AC7FDAAF-072D-4534-A3F9-2DE40D62DD74}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Zusätzliche Hinweise zur Nutzung können unter 'Hinweise' mit Stichwort und Erklärung eingefügt werden. Diese müssen auch für Laien verständlich sein. Hinweise können z.B. zu vertraglichen Bedingungen oder Besonderheiten des Datensatzes erfolgen." sqref="B30" xr:uid="{4DD816CA-8275-41A8-B3C6-1162E00F43EE}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Die Datenquelle bezeichnet das System aus dem die Daten bezogen werden können, bspw. Geodatenpool." sqref="B34" xr:uid="{4BB7D51D-AB96-4002-8175-8BC4894AA0F9}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Version des Formats dieser Excel-Vorlage" sqref="B35" xr:uid="{DE5565F3-E0DE-421D-8CEB-430905832D21}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Die Datenquelle bezeichnet das System aus dem die Daten bezogen werden können, z.B. Geodatenpool. An ihr hängen als CKAN owner_org außerdem die Bearbeitungsrechte des Metadatensatzes." sqref="B34" xr:uid="{4BB7D51D-AB96-4002-8175-8BC4894AA0F9}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Version des Formats dieser Excel-Vorlage" sqref="B36" xr:uid="{DE5565F3-E0DE-421D-8CEB-430905832D21}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Angabe über Herkunft der Daten, falls ein externer Datenurheber vorhanden ist." sqref="B14" xr:uid="{893E1363-EB8D-44CC-8DA3-7B73FBE71364}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Beschreibt den Vorgang des Geoprocessing von den Rohdaten bis zu den Fachdaten." sqref="B15" xr:uid="{ADF3A5C0-6EDA-457C-9197-256C14BF8AF4}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Legt fest ob die Daten auf der GeoServicePlattform abrufbar sind und synchronisiert werden." sqref="B22" xr:uid="{8FBB7983-3955-4A4B-B266-AF68B19178E6}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Eingeschränkter Zugriff" prompt="Ist der Zugriff auf bestimmte Gruppen/ Organisationseinheiten auf der GeoServicePlattform beschränkt, sind diese hier anzugeben (Komma als Trennzeichen)." sqref="B23" xr:uid="{2D5E2408-E8A8-4925-87FB-78E1DE201641}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Das Metadatenschema bezeichnet das Schema, in dem die Metadaten gespeichert werden." sqref="B35" xr:uid="{D70F36C4-1632-4D58-9CC9-03CC7D92E979}"/>
   </dataValidations>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="64" fitToWidth="0" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -2138,22 +2158,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="27" t="s">
+        <v>180</v>
+      </c>
+      <c r="B1" s="27" t="s">
         <v>181</v>
       </c>
-      <c r="B1" s="27" t="s">
-        <v>182</v>
-      </c>
       <c r="C1" s="27" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D1" s="27" t="s">
         <v>57</v>
       </c>
       <c r="E1" s="27" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F1" s="27" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
   </sheetData>
@@ -2180,16 +2200,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="27" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C1" s="27" t="s">
         <v>61</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
   </sheetData>
@@ -2214,16 +2234,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="27" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1" s="27" t="s">
+        <v>183</v>
+      </c>
+      <c r="C1" s="27" t="s">
         <v>87</v>
       </c>
-      <c r="B1" s="27" t="s">
-        <v>184</v>
-      </c>
-      <c r="C1" s="27" t="s">
-        <v>88</v>
-      </c>
       <c r="D1" s="27" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -2268,76 +2288,76 @@
   <sheetData>
     <row r="1" spans="1:24" s="1" customFormat="1">
       <c r="A1" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="C1" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="E1" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="M1" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="N1" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="O1" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="P1" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="Q1" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="R1" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="O1" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="P1" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="Q1" s="5" t="s">
+      <c r="S1" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="T1" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="U1" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="R1" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="S1" s="5" t="s">
+      <c r="V1" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="T1" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="U1" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="V1" s="5" t="s">
-        <v>226</v>
-      </c>
       <c r="W1" s="5" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="X1" s="5" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="2" spans="1:24">
@@ -2348,66 +2368,66 @@
         <v>23</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="K2" s="3"/>
       <c r="L2" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="N2" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="M2" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>161</v>
-      </c>
       <c r="O2" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q2" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="P2" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>80</v>
-      </c>
       <c r="R2" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="W2" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:24">
@@ -2418,70 +2438,70 @@
         <v>24</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="O3" s="2" t="s">
         <v>0</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="U3" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="V3" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="W3" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="X3" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:24">
@@ -2492,61 +2512,61 @@
         <v>25</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="V4" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="W4" s="3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="X4" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5" spans="1:24">
@@ -2557,40 +2577,40 @@
         <v>26</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="U5" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="W5" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="X5" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6" spans="1:24">
@@ -2601,40 +2621,40 @@
         <v>27</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="U6" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="W6" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="X6" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7" spans="1:24">
@@ -2645,34 +2665,34 @@
         <v>28</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="N7" s="3" t="s">
         <v>17</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="U7" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="W7" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="X7" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8" spans="1:24">
@@ -2683,34 +2703,34 @@
         <v>29</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="U8" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="W8" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="X8" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="9" spans="1:24">
@@ -2721,23 +2741,23 @@
         <v>30</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E9" s="1"/>
       <c r="G9" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="U9" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="W9" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="X9" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="10" spans="1:24">
@@ -2748,24 +2768,24 @@
         <v>31</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E10" s="1"/>
       <c r="G10" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K10" s="15"/>
       <c r="R10" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="U10" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="W10" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="X10" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="11" spans="1:24">
@@ -2776,24 +2796,24 @@
         <v>32</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E11" s="1"/>
       <c r="G11" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K11" s="15"/>
       <c r="R11" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="U11" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="W11" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="X11" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12" spans="1:24">
@@ -2804,18 +2824,18 @@
         <v>33</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E12" s="1"/>
       <c r="K12" s="15"/>
       <c r="R12" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="U12" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="W12" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" spans="1:24">
@@ -2826,15 +2846,15 @@
         <v>34</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E13" s="1"/>
       <c r="K13" s="15"/>
       <c r="R13" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="W13" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" spans="1:24">
@@ -2845,12 +2865,12 @@
         <v>35</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E14" s="1"/>
       <c r="K14" s="15"/>
       <c r="W14" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="15" spans="1:24">
@@ -2861,12 +2881,12 @@
         <v>36</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E15" s="1"/>
       <c r="K15" s="15"/>
       <c r="W15" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" spans="1:24">
@@ -2877,12 +2897,12 @@
         <v>37</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E16" s="1"/>
       <c r="K16" s="15"/>
       <c r="W16" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" spans="1:23">
@@ -2893,12 +2913,12 @@
         <v>38</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E17" s="1"/>
       <c r="K17" s="15"/>
       <c r="W17" s="3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" spans="1:23">
@@ -2909,12 +2929,12 @@
         <v>39</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E18" s="1"/>
       <c r="K18" s="15"/>
       <c r="W18" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="19" spans="1:23">
@@ -2925,12 +2945,12 @@
         <v>40</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E19" s="1"/>
       <c r="K19" s="15"/>
       <c r="W19" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="20" spans="1:23">
@@ -2938,15 +2958,15 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E20" s="1"/>
       <c r="K20" s="15"/>
       <c r="W20" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="21" spans="1:23">
@@ -2957,12 +2977,12 @@
         <v>41</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E21" s="1"/>
       <c r="K21" s="15"/>
       <c r="W21" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="22" spans="1:23">

--- a/ckanext/lhm/schemas/template_plandb.xlsx
+++ b/ckanext/lhm/schemas/template_plandb.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\home\mb\dev\ckanext-lhm\ckanext\lhm\schemas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA04A1C9-E5AE-40D9-95B4-38CAF35AC083}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C653A3C-BBA8-4C6C-9DFC-D012012B3AFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24" yWindow="384" windowWidth="23016" windowHeight="12108" tabRatio="871" xr2:uid="{EFAD0BDA-2C19-4F99-80E8-84599936D919}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="871" xr2:uid="{EFAD0BDA-2C19-4F99-80E8-84599936D919}"/>
   </bookViews>
   <sheets>
     <sheet name="Metadaten" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="268">
   <si>
     <t>nein</t>
   </si>
@@ -743,12 +743,6 @@
     <t>LHM_MD_datenquelle</t>
   </si>
   <si>
-    <t>Geodatenpool</t>
-  </si>
-  <si>
-    <t>Mobidam</t>
-  </si>
-  <si>
     <t>Attribut</t>
   </si>
   <si>
@@ -864,6 +858,15 @@
   </si>
   <si>
     <t>Metadatenschema *</t>
+  </si>
+  <si>
+    <t>GeoDatenPool</t>
+  </si>
+  <si>
+    <t>MobidaM</t>
+  </si>
+  <si>
+    <t>LHM_MD_metadatenschema</t>
   </si>
 </sst>
 </file>
@@ -1634,7 +1637,7 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="16" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B10" s="21"/>
       <c r="C10" s="12"/>
@@ -1694,7 +1697,7 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="16" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B14" s="21"/>
       <c r="C14" s="12"/>
@@ -1709,7 +1712,7 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="16" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B15" s="21"/>
       <c r="C15" s="12"/>
@@ -1724,7 +1727,7 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="16" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B16" s="21"/>
       <c r="C16" s="12"/>
@@ -1814,14 +1817,14 @@
     </row>
     <row r="22" spans="1:12">
       <c r="A22" s="16" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B22" s="21"/>
       <c r="K22" s="17"/>
     </row>
     <row r="23" spans="1:12">
       <c r="A23" s="16" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B23" s="21"/>
       <c r="K23" s="17"/>
@@ -1996,7 +1999,7 @@
     </row>
     <row r="35" spans="1:12">
       <c r="A35" s="14" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B35" s="26"/>
       <c r="C35" s="12"/>
@@ -2015,7 +2018,7 @@
         <v>199</v>
       </c>
       <c r="B36" s="26" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C36" s="12"/>
       <c r="D36" s="12"/>
@@ -2203,13 +2206,13 @@
         <v>84</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C1" s="27" t="s">
         <v>61</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
   </sheetData>
@@ -2258,7 +2261,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D073E50-F226-4B6A-BC2C-397D6C68AFA7}">
   <sheetPr codeName="Tabelle5"/>
-  <dimension ref="A1:X36"/>
+  <dimension ref="A1:Y36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="22.3984375" bestFit="1" customWidth="1"/>
@@ -2284,9 +2287,10 @@
     <col min="22" max="22" width="18.8984375" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="16.8984375" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="21.796875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="24.296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1">
+    <row r="1" spans="1:25" s="1" customFormat="1">
       <c r="A1" s="5" t="s">
         <v>201</v>
       </c>
@@ -2354,13 +2358,16 @@
         <v>225</v>
       </c>
       <c r="W1" s="5" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="X1" s="5" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="2" spans="1:24">
+        <v>236</v>
+      </c>
+      <c r="Y1" s="5" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -2421,16 +2428,19 @@
         <v>92</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>226</v>
+        <v>265</v>
       </c>
       <c r="W2" s="3" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="X2" s="2" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="3" spans="1:24">
+      <c r="Y2" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -2495,16 +2505,19 @@
         <v>91</v>
       </c>
       <c r="V3" s="2" t="s">
-        <v>227</v>
+        <v>266</v>
       </c>
       <c r="W3" s="3" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="X3" s="2" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="4" spans="1:24">
+      <c r="Y3" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
@@ -2560,16 +2573,19 @@
         <v>90</v>
       </c>
       <c r="V4" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="W4" s="3" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="X4" s="2" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="5" spans="1:24">
+      <c r="Y4" s="2" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
@@ -2607,13 +2623,13 @@
         <v>89</v>
       </c>
       <c r="W5" s="3" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="X5" s="2" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:25">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
@@ -2651,13 +2667,13 @@
         <v>192</v>
       </c>
       <c r="W6" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="X6" s="2" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:25">
       <c r="A7" s="6" t="s">
         <v>6</v>
       </c>
@@ -2683,19 +2699,19 @@
         <v>196</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="U7" s="2" t="s">
         <v>191</v>
       </c>
       <c r="W7" s="3" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="X7" s="2" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:25">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
@@ -2727,13 +2743,13 @@
         <v>193</v>
       </c>
       <c r="W8" s="3" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="X8" s="2" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
@@ -2754,13 +2770,13 @@
         <v>195</v>
       </c>
       <c r="W9" s="3" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="X9" s="2" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="10" spans="1:24">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25">
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
@@ -2776,19 +2792,19 @@
       </c>
       <c r="K10" s="15"/>
       <c r="R10" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="U10" s="2" t="s">
         <v>194</v>
       </c>
       <c r="W10" s="3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="X10" s="2" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="11" spans="1:24">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -2804,19 +2820,19 @@
       </c>
       <c r="K11" s="15"/>
       <c r="R11" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="U11" s="2" t="s">
         <v>196</v>
       </c>
       <c r="W11" s="3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="X11" s="2" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:25">
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
@@ -2835,10 +2851,10 @@
         <v>197</v>
       </c>
       <c r="W12" s="3" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25">
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
@@ -2851,13 +2867,13 @@
       <c r="E13" s="1"/>
       <c r="K13" s="15"/>
       <c r="R13" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="W13" s="3" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="14" spans="1:24">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25">
       <c r="A14" s="2" t="s">
         <v>13</v>
       </c>
@@ -2870,10 +2886,10 @@
       <c r="E14" s="1"/>
       <c r="K14" s="15"/>
       <c r="W14" s="3" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="15" spans="1:24">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25">
       <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
@@ -2886,10 +2902,10 @@
       <c r="E15" s="1"/>
       <c r="K15" s="15"/>
       <c r="W15" s="3" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="16" spans="1:24">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25">
       <c r="A16" s="2" t="s">
         <v>15</v>
       </c>
@@ -2902,7 +2918,7 @@
       <c r="E16" s="1"/>
       <c r="K16" s="15"/>
       <c r="W16" s="3" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="17" spans="1:23">
@@ -2918,7 +2934,7 @@
       <c r="E17" s="1"/>
       <c r="K17" s="15"/>
       <c r="W17" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="18" spans="1:23">
@@ -2950,7 +2966,7 @@
       <c r="E19" s="1"/>
       <c r="K19" s="15"/>
       <c r="W19" s="3" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="20" spans="1:23">
@@ -2966,7 +2982,7 @@
       <c r="E20" s="1"/>
       <c r="K20" s="15"/>
       <c r="W20" s="3" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="21" spans="1:23">
@@ -2982,7 +2998,7 @@
       <c r="E21" s="1"/>
       <c r="K21" s="15"/>
       <c r="W21" s="3" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="22" spans="1:23">
@@ -3077,7 +3093,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="ilEvpGmLo6a2O3ZAU+i9yQGGscrus6aYietO82VMOaIJdasi+nuCz4K4VGwvF5eoMx2reLQ9A/c/BCnrtsR9rw==" saltValue="4P2QQwj56WNptjDpbIU8kA==" spinCount="100000" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="KFe0QCuD87thpdz4ck4fKMGzw5Q53fIojp2KlnoFb1hbwe+Rkl3kkRpWu6YGCCD+TcLUYpZIHFUAvwG7q3nsPA==" saltValue="7iA+BZblGrXOgve/UNdGnw==" spinCount="100000" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
